--- a/Project_Submission_Folder/1_XL_Sheet_GHMIS_Master.xlsx
+++ b/Project_Submission_Folder/1_XL_Sheet_GHMIS_Master.xlsx
@@ -7249,33 +7249,7 @@
         <v>-0.6347</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Literature Reported Benchmark (Kadaladi Block)</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Spherical (nlags=8)</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>18.159</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>-0.31</v>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31"/>
     <row r="32"/>
     <row r="33">

--- a/Project_Submission_Folder/1_XL_Sheet_GHMIS_Master.xlsx
+++ b/Project_Submission_Folder/1_XL_Sheet_GHMIS_Master.xlsx
@@ -7255,7 +7255,7 @@
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>TABLE 4: LITERATURE BENCHMARK CONCORDANCE (NARAYANAN ET AL., 2021)</t>
+          <t>TABLE 4: LITERATURE BENCHMARK CONCORDANCE (NARAYANAN ET AL., 2025 SCI REP)</t>
         </is>
       </c>
     </row>
@@ -7309,20 +7309,20 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>9.2106°N, 78.3941°E</t>
+          <t>9.2107°N, 78.3941°E</t>
         </is>
       </c>
       <c r="D35" s="16" t="n">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="E35" s="16" t="n">
         <v>33.58</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>0.92</v>
+        <v>0.32</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>2.68</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36">
@@ -7338,20 +7338,20 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>9.3615°N, 78.4504°E</t>
+          <t>9.3615°N, 78.4505°E</t>
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>25.35</v>
+        <v>24.86</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>25.74</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>0.39</v>
+        <v>0.88</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>1.54</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="37">
@@ -7367,20 +7367,20 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>9.2406°N, 78.5750°E</t>
+          <t>9.2407°N, 78.5750°E</t>
         </is>
       </c>
       <c r="D37" s="16" t="n">
-        <v>31.1</v>
+        <v>30.53</v>
       </c>
       <c r="E37" s="16" t="n">
         <v>31.6</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.5</v>
+        <v>1.07</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>1.61</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="38">
@@ -7396,20 +7396,20 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>9.1747°N, 78.5096°E</t>
+          <t>9.1747°N, 78.5097°E</t>
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>40.28</v>
+        <v>39.5</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>41.35</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>1.07</v>
+        <v>1.85</v>
       </c>
       <c r="G38" s="8" t="n">
-        <v>2.65</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="39">
@@ -7429,16 +7429,16 @@
         </is>
       </c>
       <c r="D39" s="25" t="n">
-        <v>32.81</v>
+        <v>32.2</v>
       </c>
       <c r="E39" s="25" t="n">
         <v>33.07</v>
       </c>
       <c r="F39" s="25" t="n">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>2.12</v>
+        <v>3.17</v>
       </c>
     </row>
   </sheetData>
